--- a/data/the-logic-of-hypothesis-testing--factory_fills.xlsx
+++ b/data/the-logic-of-hypothesis-testing--factory_fills.xlsx
@@ -1768,7 +1768,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a quality-control sample of bottles pulled off the line.</t>
+          <t>WHAT IS CAPTURED: a quality-control sample of bottles pulled off the line (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
